--- a/TFD 3-2/Regular Assessment TFD 3-2.xlsx
+++ b/TFD 3-2/Regular Assessment TFD 3-2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Attendance\TFD 3-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF717AE7-1181-42B9-93DB-399A72487F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A02857-C8DA-4773-B775-643FC31D2105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="54">
   <si>
     <t>SL</t>
   </si>
@@ -702,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -711,11 +711,11 @@
     <col min="4" max="4" width="20.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="33.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
+    <col min="9" max="10" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>37</v>
       </c>
@@ -739,8 +739,11 @@
       <c r="I1" s="7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>36</v>
       </c>
@@ -767,8 +770,11 @@
       <c r="I2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -796,8 +802,9 @@
       <c r="I3" s="4">
         <v>46265</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -826,8 +833,9 @@
       <c r="I4" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>A4+1</f>
         <v>2</v>
@@ -857,8 +865,9 @@
       <c r="I5" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A36" si="1">A5+1</f>
         <v>3</v>
@@ -888,8 +897,9 @@
       <c r="I6" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -919,8 +929,9 @@
       <c r="I7" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -950,8 +961,9 @@
       <c r="I8" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -981,8 +993,9 @@
       <c r="I9" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -1012,8 +1025,9 @@
       <c r="I10" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -1043,8 +1057,9 @@
       <c r="I11" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -1074,8 +1089,9 @@
       <c r="I12" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -1105,8 +1121,9 @@
       <c r="I13" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -1136,8 +1153,9 @@
       <c r="I14" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -1167,8 +1185,9 @@
       <c r="I15" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -1198,8 +1217,9 @@
       <c r="I16" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -1229,8 +1249,9 @@
       <c r="I17" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -1260,8 +1281,9 @@
       <c r="I18" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -1291,8 +1313,9 @@
       <c r="I19" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -1322,8 +1345,9 @@
       <c r="I20" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -1353,8 +1377,9 @@
       <c r="I21" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -1384,8 +1409,9 @@
       <c r="I22" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -1415,8 +1441,9 @@
       <c r="I23" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -1446,8 +1473,9 @@
       <c r="I24" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -1477,8 +1505,9 @@
       <c r="I25" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -1508,8 +1537,9 @@
       <c r="I26" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -1539,8 +1569,9 @@
       <c r="I27" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -1570,8 +1601,9 @@
       <c r="I28" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -1601,8 +1633,9 @@
       <c r="I29" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -1632,8 +1665,9 @@
       <c r="I30" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -1663,8 +1697,9 @@
       <c r="I31" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -1694,8 +1729,9 @@
       <c r="I32" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -1725,8 +1761,9 @@
       <c r="I33" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -1756,8 +1793,9 @@
       <c r="I34" s="9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -1787,8 +1825,9 @@
       <c r="I35" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -1818,6 +1857,7 @@
       <c r="I36" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="J36" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/TFD 3-2/Regular Assessment TFD 3-2.xlsx
+++ b/TFD 3-2/Regular Assessment TFD 3-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A02857-C8DA-4773-B775-643FC31D2105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3AC23A-1104-42C5-9439-8C33390F607F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="55">
   <si>
     <t>SL</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>Color &amp; Weave Effects</t>
+  </si>
+  <si>
+    <t>JOBAYER AHAMMAED</t>
   </si>
 </sst>
 </file>
@@ -702,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:X37"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -712,10 +715,11 @@
     <col min="5" max="5" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="33.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="2"/>
+    <col min="11" max="11" width="10.6640625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>37</v>
       </c>
@@ -742,8 +746,22 @@
       <c r="J1" s="7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>36</v>
       </c>
@@ -759,22 +777,83 @@
         <v>1</v>
       </c>
       <c r="F2" s="8">
+        <f>E2+1</f>
         <v>2</v>
       </c>
       <c r="G2" s="8">
+        <f t="shared" ref="G2:X2" si="0">F2+1</f>
         <v>3</v>
       </c>
       <c r="H2" s="8">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="I2" s="8">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="J2" s="8">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K2" s="8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="L2" s="8">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="M2" s="8">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="N2" s="8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="O2" s="8">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="P2" s="8">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="Q2" s="8">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="R2" s="8">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="S2" s="8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="T2" s="8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="U2" s="8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="V2" s="8">
+        <f>U2+1</f>
+        <v>18</v>
+      </c>
+      <c r="W2" s="8">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="X2" s="8">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -802,9 +881,25 @@
       <c r="I3" s="4">
         <v>46265</v>
       </c>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="4">
+        <v>46271</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -833,9 +928,25 @@
       <c r="I4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>A4+1</f>
         <v>2</v>
@@ -847,7 +958,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="10">
-        <f t="shared" ref="D5:D36" si="0">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
+        <f t="shared" ref="D5:D37" si="1">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -865,11 +976,27 @@
       <c r="I5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A36" si="1">A5+1</f>
+        <f t="shared" ref="A6:A37" si="2">A5+1</f>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -879,7 +1006,7 @@
         <v>6</v>
       </c>
       <c r="D6" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -897,11 +1024,27 @@
       <c r="I6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="B7" s="1">
@@ -911,8 +1054,8 @@
         <v>7</v>
       </c>
       <c r="D7" s="10">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>40</v>
@@ -929,11 +1072,27 @@
       <c r="I7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -943,7 +1102,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -961,11 +1120,27 @@
       <c r="I8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="B9" s="1">
@@ -975,7 +1150,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -993,11 +1168,27 @@
       <c r="I9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -1007,8 +1198,8 @@
         <v>10</v>
       </c>
       <c r="D10" s="10">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>40</v>
@@ -1025,11 +1216,27 @@
       <c r="I10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B11" s="1">
@@ -1039,8 +1246,8 @@
         <v>11</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>39</v>
@@ -1057,11 +1264,27 @@
       <c r="I11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B12" s="1">
@@ -1071,7 +1294,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1089,11 +1312,27 @@
       <c r="I12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
@@ -1103,8 +1342,8 @@
         <v>13</v>
       </c>
       <c r="D13" s="10">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>40</v>
@@ -1121,11 +1360,27 @@
       <c r="I13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B14" s="1">
@@ -1135,8 +1390,8 @@
         <v>14</v>
       </c>
       <c r="D14" s="10">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>40</v>
@@ -1153,11 +1408,27 @@
       <c r="I14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="B15" s="1">
@@ -1167,8 +1438,8 @@
         <v>15</v>
       </c>
       <c r="D15" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>39</v>
@@ -1185,11 +1456,27 @@
       <c r="I15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="B16" s="1">
@@ -1199,8 +1486,8 @@
         <v>16</v>
       </c>
       <c r="D16" s="10">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>40</v>
@@ -1217,11 +1504,27 @@
       <c r="I16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="B17" s="1">
@@ -1231,7 +1534,7 @@
         <v>17</v>
       </c>
       <c r="D17" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1249,11 +1552,27 @@
       <c r="I17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="B18" s="1">
@@ -1263,8 +1582,8 @@
         <v>18</v>
       </c>
       <c r="D18" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>40</v>
@@ -1281,11 +1600,27 @@
       <c r="I18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="B19" s="1">
@@ -1295,8 +1630,8 @@
         <v>19</v>
       </c>
       <c r="D19" s="10">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>40</v>
@@ -1313,11 +1648,27 @@
       <c r="I19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J19" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -1327,7 +1678,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1345,11 +1696,27 @@
       <c r="I20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="B21" s="1">
@@ -1359,8 +1726,8 @@
         <v>21</v>
       </c>
       <c r="D21" s="10">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>39</v>
@@ -1377,11 +1744,27 @@
       <c r="I21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="B22" s="1">
@@ -1391,8 +1774,8 @@
         <v>22</v>
       </c>
       <c r="D22" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>39</v>
@@ -1409,11 +1792,27 @@
       <c r="I22" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="B23" s="1">
@@ -1423,8 +1822,8 @@
         <v>23</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>39</v>
@@ -1441,11 +1840,27 @@
       <c r="I23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="B24" s="1">
@@ -1455,8 +1870,8 @@
         <v>3</v>
       </c>
       <c r="D24" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>39</v>
@@ -1473,11 +1888,27 @@
       <c r="I24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J24" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="B25" s="1">
@@ -1487,8 +1918,8 @@
         <v>24</v>
       </c>
       <c r="D25" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>39</v>
@@ -1505,11 +1936,27 @@
       <c r="I25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="B26" s="1">
@@ -1519,8 +1966,8 @@
         <v>25</v>
       </c>
       <c r="D26" s="10">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>40</v>
@@ -1537,11 +1984,27 @@
       <c r="I26" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J26" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="B27" s="1">
@@ -1551,8 +2014,8 @@
         <v>26</v>
       </c>
       <c r="D27" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>39</v>
@@ -1569,11 +2032,27 @@
       <c r="I27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J27" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="B28" s="1">
@@ -1583,8 +2062,8 @@
         <v>27</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>40</v>
@@ -1601,11 +2080,27 @@
       <c r="I28" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J28" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="B29" s="1">
@@ -1615,8 +2110,8 @@
         <v>28</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>39</v>
@@ -1633,11 +2128,27 @@
       <c r="I29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="B30" s="1">
@@ -1647,8 +2158,8 @@
         <v>29</v>
       </c>
       <c r="D30" s="10">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>39</v>
@@ -1665,11 +2176,27 @@
       <c r="I30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="B31" s="1">
@@ -1679,8 +2206,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>39</v>
@@ -1697,11 +2224,27 @@
       <c r="I31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J31" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="B32" s="1">
@@ -1711,7 +2254,7 @@
         <v>31</v>
       </c>
       <c r="D32" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -1729,11 +2272,27 @@
       <c r="I32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="B33" s="1">
@@ -1743,7 +2302,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -1761,11 +2320,27 @@
       <c r="I33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="B34" s="1">
@@ -1775,8 +2350,8 @@
         <v>33</v>
       </c>
       <c r="D34" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>39</v>
@@ -1793,11 +2368,27 @@
       <c r="I34" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="B35" s="1">
@@ -1807,8 +2398,8 @@
         <v>34</v>
       </c>
       <c r="D35" s="10">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>39</v>
@@ -1825,11 +2416,27 @@
       <c r="I35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="B36" s="1">
@@ -1839,8 +2446,8 @@
         <v>35</v>
       </c>
       <c r="D36" s="10">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>40</v>
@@ -1857,14 +2464,78 @@
       <c r="I36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J36" s="1"/>
+      <c r="J36" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>202116031</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="10">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D36">
+  <conditionalFormatting sqref="D4:D37">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>

--- a/TFD 3-2/Regular Assessment TFD 3-2.xlsx
+++ b/TFD 3-2/Regular Assessment TFD 3-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3AC23A-1104-42C5-9439-8C33390F607F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31074112-8EDF-4420-98C8-F236562DA813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -715,7 +715,7 @@
     <col min="5" max="5" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="33.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -884,7 +884,9 @@
       <c r="J3" s="4">
         <v>46271</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="K3" s="4">
+        <v>46274</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>

--- a/TFD 3-2/Regular Assessment TFD 3-2.xlsx
+++ b/TFD 3-2/Regular Assessment TFD 3-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31074112-8EDF-4420-98C8-F236562DA813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCEBC97-0934-4A8F-A631-A5FADE339256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="56">
   <si>
     <t>SL</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>JOBAYER AHAMMAED</t>
+  </si>
+  <si>
+    <t>10.40 AM - 11.30 AM</t>
   </si>
 </sst>
 </file>
@@ -261,7 +264,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,6 +324,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -350,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -401,6 +410,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -711,7 +723,7 @@
     <col min="1" max="1" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="33.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -746,7 +758,9 @@
       <c r="J1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="7"/>
+      <c r="K1" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
@@ -933,7 +947,9 @@
       <c r="J4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -981,7 +997,9 @@
       <c r="J5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -1009,7 +1027,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>40</v>
@@ -1029,7 +1047,9 @@
       <c r="J6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -1057,7 +1077,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>40</v>
@@ -1077,7 +1097,9 @@
       <c r="J7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -1125,7 +1147,9 @@
       <c r="J8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1173,7 +1197,9 @@
       <c r="J9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -1201,7 +1227,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>40</v>
@@ -1221,7 +1247,9 @@
       <c r="J10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -1237,7 +1265,7 @@
       <c r="X10" s="1"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="A11" s="18">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -1249,7 +1277,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>39</v>
@@ -1269,7 +1297,9 @@
       <c r="J11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1317,7 +1347,9 @@
       <c r="J12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -1345,7 +1377,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>40</v>
@@ -1365,7 +1397,9 @@
       <c r="J13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -1393,7 +1427,7 @@
       </c>
       <c r="D14" s="10">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>40</v>
@@ -1413,7 +1447,9 @@
       <c r="J14" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -1441,7 +1477,7 @@
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>39</v>
@@ -1461,7 +1497,9 @@
       <c r="J15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1489,7 +1527,7 @@
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>40</v>
@@ -1509,7 +1547,9 @@
       <c r="J16" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -1557,7 +1597,9 @@
       <c r="J17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -1585,7 +1627,7 @@
       </c>
       <c r="D18" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>40</v>
@@ -1605,7 +1647,9 @@
       <c r="J18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="K18" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -1633,7 +1677,7 @@
       </c>
       <c r="D19" s="10">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>40</v>
@@ -1653,7 +1697,9 @@
       <c r="J19" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -1701,7 +1747,9 @@
       <c r="J20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -1729,7 +1777,7 @@
       </c>
       <c r="D21" s="10">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>39</v>
@@ -1749,7 +1797,9 @@
       <c r="J21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -1777,7 +1827,7 @@
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>39</v>
@@ -1797,7 +1847,9 @@
       <c r="J22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -1825,7 +1877,7 @@
       </c>
       <c r="D23" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>39</v>
@@ -1845,7 +1897,9 @@
       <c r="J23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -1873,7 +1927,7 @@
       </c>
       <c r="D24" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>39</v>
@@ -1893,7 +1947,9 @@
       <c r="J24" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -1921,7 +1977,7 @@
       </c>
       <c r="D25" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>39</v>
@@ -1941,7 +1997,9 @@
       <c r="J25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -1969,7 +2027,7 @@
       </c>
       <c r="D26" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>40</v>
@@ -1989,7 +2047,9 @@
       <c r="J26" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -2017,7 +2077,7 @@
       </c>
       <c r="D27" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>39</v>
@@ -2037,7 +2097,9 @@
       <c r="J27" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -2065,7 +2127,7 @@
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>40</v>
@@ -2085,7 +2147,9 @@
       <c r="J28" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -2113,7 +2177,7 @@
       </c>
       <c r="D29" s="10">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>39</v>
@@ -2133,7 +2197,9 @@
       <c r="J29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -2161,7 +2227,7 @@
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>39</v>
@@ -2181,7 +2247,9 @@
       <c r="J30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -2209,7 +2277,7 @@
       </c>
       <c r="D31" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>39</v>
@@ -2229,7 +2297,9 @@
       <c r="J31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K31" s="1"/>
+      <c r="K31" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -2277,7 +2347,9 @@
       <c r="J32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K32" s="1"/>
+      <c r="K32" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -2325,7 +2397,9 @@
       <c r="J33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -2353,7 +2427,7 @@
       </c>
       <c r="D34" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>39</v>
@@ -2373,7 +2447,9 @@
       <c r="J34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -2401,7 +2477,7 @@
       </c>
       <c r="D35" s="10">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>39</v>
@@ -2421,7 +2497,9 @@
       <c r="J35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -2449,7 +2527,7 @@
       </c>
       <c r="D36" s="10">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>40</v>
@@ -2469,7 +2547,9 @@
       <c r="J36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
@@ -2497,7 +2577,7 @@
       </c>
       <c r="D37" s="10">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>39</v>
@@ -2517,7 +2597,9 @@
       <c r="J37" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K37" s="1"/>
+      <c r="K37" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>

--- a/TFD 3-2/Regular Assessment TFD 3-2.xlsx
+++ b/TFD 3-2/Regular Assessment TFD 3-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCEBC97-0934-4A8F-A631-A5FADE339256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030EF7F3-8B06-4610-AE11-9244D2D50DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -406,13 +406,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -420,7 +420,37 @@
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -732,10 +762,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="6" t="s">
         <v>38</v>
       </c>
@@ -1265,7 +1295,7 @@
       <c r="X10" s="1"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="18">
+      <c r="A11" s="16">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -2620,11 +2650,15 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D37">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>0.6</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
+      <formula>0.6</formula>
+      <formula>0.89</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2647,10 +2681,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="6" t="s">
         <v>38</v>
       </c>
@@ -2660,10 +2694,10 @@
       <c r="E1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="17"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -2682,8 +2716,8 @@
       <c r="E2" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">

--- a/TFD 3-2/Regular Assessment TFD 3-2.xlsx
+++ b/TFD 3-2/Regular Assessment TFD 3-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030EF7F3-8B06-4610-AE11-9244D2D50DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1965D3E5-E6A4-4CCA-938B-9C0DF3887BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-2 Attendance'!$A$3:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-2 Attendance'!$A$3:$J$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="57">
   <si>
     <t>SL</t>
   </si>
@@ -207,6 +229,9 @@
   </si>
   <si>
     <t>10.40 AM - 11.30 AM</t>
+  </si>
+  <si>
+    <t>Marks</t>
   </si>
 </sst>
 </file>
@@ -420,7 +445,17 @@
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -428,6 +463,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -443,6 +488,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -453,11 +508,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -747,21 +802,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="33.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="33.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.44140625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>37</v>
       </c>
@@ -770,29 +828,31 @@
         <v>38</v>
       </c>
       <c r="D1" s="6"/>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
+      <c r="M1" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
@@ -804,8 +864,9 @@
       <c r="V1" s="7"/>
       <c r="W1" s="7"/>
       <c r="X1" s="7"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y1" s="7"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>36</v>
       </c>
@@ -817,87 +878,88 @@
         <v>41</v>
       </c>
       <c r="D2" s="6"/>
-      <c r="E2" s="8">
+      <c r="E2" s="6"/>
+      <c r="F2" s="8">
         <v>1</v>
       </c>
-      <c r="F2" s="8">
-        <f>E2+1</f>
+      <c r="G2" s="8">
+        <f>F2+1</f>
         <v>2</v>
       </c>
-      <c r="G2" s="8">
-        <f t="shared" ref="G2:X2" si="0">F2+1</f>
+      <c r="H2" s="8">
+        <f t="shared" ref="H2:Y2" si="0">G2+1</f>
         <v>3</v>
       </c>
-      <c r="H2" s="8">
+      <c r="I2" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I2" s="8">
-        <f t="shared" si="0"/>
+      <c r="J2" s="8">
+        <f>I2+1</f>
         <v>5</v>
       </c>
-      <c r="J2" s="8">
+      <c r="K2" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K2" s="8">
+      <c r="L2" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="L2" s="8">
+      <c r="M2" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M2" s="8">
+      <c r="N2" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="N2" s="8">
+      <c r="O2" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O2" s="8">
+      <c r="P2" s="8">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="P2" s="8">
+      <c r="Q2" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="R2" s="8">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="R2" s="8">
+      <c r="S2" s="8">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="S2" s="8">
+      <c r="T2" s="8">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="T2" s="8">
+      <c r="U2" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U2" s="8">
+      <c r="V2" s="8">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="V2" s="8">
-        <f>U2+1</f>
+      <c r="W2" s="8">
+        <f>V2+1</f>
         <v>18</v>
       </c>
-      <c r="W2" s="8">
+      <c r="X2" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="X2" s="8">
+      <c r="Y2" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -910,11 +972,11 @@
       <c r="D3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4">
         <v>46258</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46259</v>
       </c>
       <c r="G3" s="4">
         <v>46259</v>
@@ -923,16 +985,20 @@
         <v>46259</v>
       </c>
       <c r="I3" s="4">
+        <v>46259</v>
+      </c>
+      <c r="J3" s="4">
         <v>46265</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <v>46271</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>46274</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="M3" s="4">
+        <v>46278</v>
+      </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -944,8 +1010,9 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y3" s="4"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -956,11 +1023,12 @@
         <v>4</v>
       </c>
       <c r="D4" s="10">
-        <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
+        <f t="shared" ref="D4:D37" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>40</v>
+      <c r="E4" s="1" cm="1">
+        <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>40</v>
@@ -980,8 +1048,12 @@
       <c r="K4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="L4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -993,8 +1065,9 @@
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y4" s="1"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>A4+1</f>
         <v>2</v>
@@ -1006,11 +1079,12 @@
         <v>5</v>
       </c>
       <c r="D5" s="10">
-        <f t="shared" ref="D5:D37" si="1">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>40</v>
+      <c r="E5" s="1" cm="1">
+        <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>40</v>
@@ -1030,8 +1104,12 @@
       <c r="K5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1043,8 +1121,9 @@
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y5" s="1"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A37" si="2">A5+1</f>
         <v>3</v>
@@ -1057,10 +1136,11 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>0.875</v>
+      </c>
+      <c r="E6" s="1" cm="1">
+        <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>40</v>
@@ -1077,11 +1157,15 @@
       <c r="J6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1093,8 +1177,9 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y6" s="1"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -1107,10 +1192,11 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>0.875</v>
+      </c>
+      <c r="E7" s="1" cm="1">
+        <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>40</v>
@@ -1118,11 +1204,11 @@
       <c r="G7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>40</v>
+      <c r="H7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>40</v>
@@ -1130,8 +1216,12 @@
       <c r="K7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -1143,8 +1233,9 @@
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y7" s="1"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1159,8 +1250,9 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>40</v>
+      <c r="E8" s="1" cm="1">
+        <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>40</v>
@@ -1180,8 +1272,12 @@
       <c r="K8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1193,8 +1289,9 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y8" s="1"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1209,8 +1306,9 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>40</v>
+      <c r="E9" s="1" cm="1">
+        <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>40</v>
@@ -1230,8 +1328,12 @@
       <c r="K9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -1243,8 +1345,9 @@
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y9" s="1"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -1257,10 +1360,11 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>40</v>
+        <v>0.625</v>
+      </c>
+      <c r="E10" s="1" cm="1">
+        <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>40</v>
@@ -1271,8 +1375,8 @@
       <c r="H10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>39</v>
+      <c r="I10" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>39</v>
@@ -1280,8 +1384,12 @@
       <c r="K10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="L10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1293,8 +1401,9 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y10" s="1"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="16">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -1307,31 +1416,36 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>39</v>
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="1" cm="1">
+        <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
+        <v>0</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>40</v>
+      <c r="G11" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>40</v>
+      <c r="I11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -1343,8 +1457,9 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y11" s="1"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -1359,8 +1474,9 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>40</v>
+      <c r="E12" s="1" cm="1">
+        <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>40</v>
@@ -1380,8 +1496,12 @@
       <c r="K12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -1393,8 +1513,9 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y12" s="1"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -1407,19 +1528,20 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>39</v>
+        <v>0.375</v>
+      </c>
+      <c r="E13" s="1" cm="1">
+        <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>39</v>
@@ -1430,8 +1552,12 @@
       <c r="K13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+      <c r="L13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
@@ -1443,8 +1569,9 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y13" s="1"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1457,10 +1584,11 @@
       </c>
       <c r="D14" s="10">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>0.875</v>
+      </c>
+      <c r="E14" s="1" cm="1">
+        <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>40</v>
@@ -1474,14 +1602,18 @@
       <c r="I14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
@@ -1493,8 +1625,9 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y14" s="1"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -1507,16 +1640,17 @@
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>39</v>
+        <v>0.625</v>
+      </c>
+      <c r="E15" s="1" cm="1">
+        <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>40</v>
+      <c r="G15" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>40</v>
@@ -1524,14 +1658,18 @@
       <c r="I15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
@@ -1543,8 +1681,9 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y15" s="1"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -1557,10 +1696,11 @@
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>40</v>
+        <v>0.875</v>
+      </c>
+      <c r="E16" s="1" cm="1">
+        <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>40</v>
@@ -1574,14 +1714,18 @@
       <c r="I16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J16" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
@@ -1593,8 +1737,9 @@
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y16" s="1"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -1609,8 +1754,9 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>40</v>
+      <c r="E17" s="1" cm="1">
+        <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>40</v>
@@ -1630,8 +1776,12 @@
       <c r="K17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -1643,8 +1793,9 @@
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y17" s="1"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1657,31 +1808,36 @@
       </c>
       <c r="D18" s="10">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>40</v>
+        <v>0.5</v>
+      </c>
+      <c r="E18" s="1" cm="1">
+        <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>39</v>
+      <c r="I18" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
+      <c r="K18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -1693,8 +1849,9 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y18" s="1"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -1707,10 +1864,11 @@
       </c>
       <c r="D19" s="10">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>40</v>
+        <v>0.875</v>
+      </c>
+      <c r="E19" s="1" cm="1">
+        <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>40</v>
@@ -1724,14 +1882,18 @@
       <c r="I19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J19" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1743,8 +1905,9 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y19" s="1"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -1759,8 +1922,9 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>40</v>
+      <c r="E20" s="1" cm="1">
+        <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>40</v>
@@ -1780,8 +1944,12 @@
       <c r="K20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -1793,8 +1961,9 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y20" s="1"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -1807,13 +1976,14 @@
       </c>
       <c r="D21" s="10">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>40</v>
+        <v>0.875</v>
+      </c>
+      <c r="E21" s="1" cm="1">
+        <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
+        <v>6</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>40</v>
@@ -1830,8 +2000,12 @@
       <c r="K21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -1843,8 +2017,9 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y21" s="1"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -1857,13 +2032,14 @@
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>40</v>
+        <v>0.75</v>
+      </c>
+      <c r="E22" s="1" cm="1">
+        <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>40</v>
@@ -1871,17 +2047,21 @@
       <c r="H22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>40</v>
+      <c r="I22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -1893,8 +2073,9 @@
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y22" s="1"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -1907,16 +2088,17 @@
       </c>
       <c r="D23" s="10">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>39</v>
+        <v>0.75</v>
+      </c>
+      <c r="E23" s="1" cm="1">
+        <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>40</v>
+      <c r="G23" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>40</v>
@@ -1930,8 +2112,12 @@
       <c r="K23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -1943,8 +2129,9 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y23" s="1"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -1957,16 +2144,17 @@
       </c>
       <c r="D24" s="10">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>39</v>
+        <v>0.625</v>
+      </c>
+      <c r="E24" s="1" cm="1">
+        <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>40</v>
+      <c r="G24" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>40</v>
@@ -1974,14 +2162,18 @@
       <c r="I24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J24" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -1993,8 +2185,9 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y24" s="1"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -2007,16 +2200,17 @@
       </c>
       <c r="D25" s="10">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>39</v>
+        <v>0.625</v>
+      </c>
+      <c r="E25" s="1" cm="1">
+        <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>40</v>
+      <c r="G25" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>40</v>
@@ -2030,8 +2224,12 @@
       <c r="K25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -2043,8 +2241,9 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y25" s="1"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2057,10 +2256,11 @@
       </c>
       <c r="D26" s="10">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>40</v>
+        <v>0.75</v>
+      </c>
+      <c r="E26" s="1" cm="1">
+        <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>40</v>
@@ -2071,17 +2271,21 @@
       <c r="H26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>39</v>
+      <c r="I26" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
+      <c r="K26" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -2093,8 +2297,9 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y26" s="1"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2107,16 +2312,17 @@
       </c>
       <c r="D27" s="10">
         <f t="shared" si="1"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>39</v>
+        <v>0.375</v>
+      </c>
+      <c r="E27" s="1" cm="1">
+        <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
+        <v>0</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>40</v>
+      <c r="G27" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>40</v>
@@ -2124,14 +2330,18 @@
       <c r="I27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J27" s="9" t="s">
-        <v>39</v>
+      <c r="J27" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
+      <c r="L27" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -2143,8 +2353,9 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y27" s="1"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2157,10 +2368,11 @@
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>40</v>
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="1" cm="1">
+        <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>40</v>
@@ -2171,17 +2383,21 @@
       <c r="H28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>39</v>
+      <c r="I28" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
+      <c r="K28" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
@@ -2193,8 +2409,9 @@
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y28" s="1"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2207,13 +2424,14 @@
       </c>
       <c r="D29" s="10">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>40</v>
+        <v>0.75</v>
+      </c>
+      <c r="E29" s="1" cm="1">
+        <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>40</v>
@@ -2230,8 +2448,12 @@
       <c r="K29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
+      <c r="L29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
@@ -2243,8 +2465,9 @@
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y29" s="1"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2257,13 +2480,14 @@
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>40</v>
+        <v>0.75</v>
+      </c>
+      <c r="E30" s="1" cm="1">
+        <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>40</v>
@@ -2274,14 +2498,18 @@
       <c r="I30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
@@ -2293,8 +2521,9 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y30" s="1"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2307,16 +2536,17 @@
       </c>
       <c r="D31" s="10">
         <f t="shared" si="1"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>39</v>
+        <v>0.375</v>
+      </c>
+      <c r="E31" s="1" cm="1">
+        <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
+        <v>0</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>40</v>
+      <c r="G31" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>40</v>
@@ -2324,14 +2554,18 @@
       <c r="I31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>39</v>
+      <c r="J31" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
+      <c r="L31" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
@@ -2343,8 +2577,9 @@
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y31" s="1"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -2359,8 +2594,9 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>40</v>
+      <c r="E32" s="1" cm="1">
+        <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>40</v>
@@ -2380,8 +2616,12 @@
       <c r="K32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
+      <c r="L32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
@@ -2393,8 +2633,9 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y32" s="1"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -2407,10 +2648,11 @@
       </c>
       <c r="D33" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>40</v>
+        <v>0.875</v>
+      </c>
+      <c r="E33" s="1" cm="1">
+        <f t="array" ref="E33">_xlfn.IFS(D33&gt;=90%,7.5,D33&gt;=80%,6,D33&gt;=70%,4.5,D33&gt;=60%,3,D33&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>40</v>
@@ -2430,8 +2672,12 @@
       <c r="K33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -2443,8 +2689,9 @@
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y33" s="1"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -2457,13 +2704,14 @@
       </c>
       <c r="D34" s="10">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>40</v>
+        <v>0.625</v>
+      </c>
+      <c r="E34" s="1" cm="1">
+        <f t="array" ref="E34">_xlfn.IFS(D34&gt;=90%,7.5,D34&gt;=80%,6,D34&gt;=70%,4.5,D34&gt;=60%,3,D34&lt;60%,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>40</v>
@@ -2471,17 +2719,21 @@
       <c r="H34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I34" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>40</v>
+      <c r="I34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -2493,8 +2745,9 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y34" s="1"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -2507,16 +2760,17 @@
       </c>
       <c r="D35" s="10">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>39</v>
+        <v>0.625</v>
+      </c>
+      <c r="E35" s="1" cm="1">
+        <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>40</v>
+      <c r="G35" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>40</v>
@@ -2530,8 +2784,12 @@
       <c r="K35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
+      <c r="L35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
@@ -2543,8 +2801,9 @@
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y35" s="1"/>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -2557,10 +2816,11 @@
       </c>
       <c r="D36" s="10">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>40</v>
+        <v>0.875</v>
+      </c>
+      <c r="E36" s="1" cm="1">
+        <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>40</v>
@@ -2574,14 +2834,18 @@
       <c r="I36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J36" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
+      <c r="J36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
@@ -2593,8 +2857,9 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y36" s="1"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -2607,10 +2872,11 @@
       </c>
       <c r="D37" s="10">
         <f t="shared" si="1"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>39</v>
+        <v>0.125</v>
+      </c>
+      <c r="E37" s="1" cm="1">
+        <f t="array" ref="E37">_xlfn.IFS(D37&gt;=90%,7.5,D37&gt;=80%,6,D37&gt;=70%,4.5,D37&gt;=60%,3,D37&lt;60%,0)</f>
+        <v>0</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>39</v>
@@ -2624,14 +2890,18 @@
       <c r="I37" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
+      <c r="J37" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -2643,22 +2913,46 @@
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:J3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="greaterThan">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="between">
+      <formula>0.6</formula>
+      <formula>0.89</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D4:D37">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>0.6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.9</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D37">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="between">
+      <formula>0.6</formula>
+      <formula>0.79</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
-      <formula>0.6</formula>
-      <formula>0.89</formula>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="greaterThan">
+      <formula>0.79</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E37">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>2</formula>
+      <formula>5.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TFD 3-2/Regular Assessment TFD 3-2.xlsx
+++ b/TFD 3-2/Regular Assessment TFD 3-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1965D3E5-E6A4-4CCA-938B-9C0DF3887BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ACFB45-9F72-4028-A14D-CDB96C0B8E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="57">
   <si>
     <t>SL</t>
   </si>
@@ -815,8 +815,10 @@
     <col min="10" max="11" width="32.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.44140625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="2"/>
+    <col min="14" max="14" width="36.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="25" width="16.21875" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -853,8 +855,12 @@
       <c r="M1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="N1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
@@ -999,8 +1005,12 @@
       <c r="M3" s="4">
         <v>46278</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="N3" s="4">
+        <v>46281</v>
+      </c>
+      <c r="O3" s="4">
+        <v>46285</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -1024,7 +1034,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" ref="D4:D37" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
@@ -1054,8 +1064,12 @@
       <c r="M4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
+      <c r="N4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -1080,7 +1094,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
@@ -1110,8 +1124,12 @@
       <c r="M5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+      <c r="N5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -1136,11 +1154,11 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>40</v>
@@ -1166,8 +1184,12 @@
       <c r="M6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
+      <c r="N6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
@@ -1192,11 +1214,11 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="1" cm="1">
         <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>40</v>
@@ -1222,8 +1244,12 @@
       <c r="M7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
@@ -1248,7 +1274,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E8" s="1" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
@@ -1278,8 +1304,12 @@
       <c r="M8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
@@ -1304,7 +1334,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
@@ -1334,8 +1364,12 @@
       <c r="M9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
+      <c r="N9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -1360,11 +1394,11 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.7</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>40</v>
@@ -1390,8 +1424,12 @@
       <c r="M10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -1446,8 +1484,12 @@
       <c r="M11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -1502,8 +1544,12 @@
       <c r="M12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1528,7 +1574,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="1" cm="1">
         <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
@@ -1558,8 +1604,12 @@
       <c r="M13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -1584,11 +1634,11 @@
       </c>
       <c r="D14" s="10">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>40</v>
@@ -1614,8 +1664,12 @@
       <c r="M14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
@@ -1640,7 +1694,7 @@
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="E15" s="1" cm="1">
         <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
@@ -1670,8 +1724,12 @@
       <c r="M15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -1696,11 +1754,11 @@
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="E16" s="1" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>40</v>
@@ -1726,8 +1784,12 @@
       <c r="M16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
+      <c r="N16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
@@ -1782,8 +1844,12 @@
       <c r="M17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
+      <c r="N17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
@@ -1838,8 +1904,12 @@
       <c r="M18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
+      <c r="N18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -1864,7 +1934,7 @@
       </c>
       <c r="D19" s="10">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.8</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1894,8 +1964,12 @@
       <c r="M19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -1920,7 +1994,7 @@
       </c>
       <c r="D20" s="10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E20" s="1" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
@@ -1950,8 +2024,12 @@
       <c r="M20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
@@ -1976,11 +2054,11 @@
       </c>
       <c r="D21" s="10">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.9</v>
       </c>
       <c r="E21" s="1" cm="1">
         <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>39</v>
@@ -2006,8 +2084,12 @@
       <c r="M21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
@@ -2032,7 +2114,7 @@
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E22" s="1" cm="1">
         <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
@@ -2062,8 +2144,12 @@
       <c r="M22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -2088,7 +2174,7 @@
       </c>
       <c r="D23" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
@@ -2118,8 +2204,12 @@
       <c r="M23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -2144,7 +2234,7 @@
       </c>
       <c r="D24" s="10">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
@@ -2174,8 +2264,12 @@
       <c r="M24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
+      <c r="N24" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -2200,11 +2294,11 @@
       </c>
       <c r="D25" s="10">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.7</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>39</v>
@@ -2230,8 +2324,12 @@
       <c r="M25" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
+      <c r="N25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -2256,7 +2354,7 @@
       </c>
       <c r="D26" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E26" s="1" cm="1">
         <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
@@ -2286,8 +2384,12 @@
       <c r="M26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
+      <c r="N26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
@@ -2312,7 +2414,7 @@
       </c>
       <c r="D27" s="10">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
@@ -2342,8 +2444,12 @@
       <c r="M27" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
+      <c r="N27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
@@ -2368,7 +2474,7 @@
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
@@ -2398,8 +2504,12 @@
       <c r="M28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
+      <c r="N28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
@@ -2424,11 +2534,11 @@
       </c>
       <c r="D29" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>39</v>
@@ -2454,8 +2564,12 @@
       <c r="M29" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
@@ -2480,7 +2594,7 @@
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
@@ -2510,8 +2624,12 @@
       <c r="M30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
+      <c r="N30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
@@ -2536,7 +2654,7 @@
       </c>
       <c r="D31" s="10">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
@@ -2566,8 +2684,12 @@
       <c r="M31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
+      <c r="N31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
@@ -2622,8 +2744,12 @@
       <c r="M32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
+      <c r="N32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
@@ -2648,7 +2774,7 @@
       </c>
       <c r="D33" s="10">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.8</v>
       </c>
       <c r="E33" s="1" cm="1">
         <f t="array" ref="E33">_xlfn.IFS(D33&gt;=90%,7.5,D33&gt;=80%,6,D33&gt;=70%,4.5,D33&gt;=60%,3,D33&lt;60%,0)</f>
@@ -2678,8 +2804,12 @@
       <c r="M33" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
+      <c r="N33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
@@ -2704,7 +2834,7 @@
       </c>
       <c r="D34" s="10">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="E34" s="1" cm="1">
         <f t="array" ref="E34">_xlfn.IFS(D34&gt;=90%,7.5,D34&gt;=80%,6,D34&gt;=70%,4.5,D34&gt;=60%,3,D34&lt;60%,0)</f>
@@ -2734,8 +2864,12 @@
       <c r="M34" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
+      <c r="N34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
@@ -2760,7 +2894,7 @@
       </c>
       <c r="D35" s="10">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
@@ -2790,8 +2924,12 @@
       <c r="M35" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
+      <c r="N35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
@@ -2816,11 +2954,11 @@
       </c>
       <c r="D36" s="10">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.7</v>
       </c>
       <c r="E36" s="1" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>40</v>
@@ -2846,8 +2984,12 @@
       <c r="M36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+      <c r="N36" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
@@ -2872,7 +3014,7 @@
       </c>
       <c r="D37" s="10">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="E37" s="1" cm="1">
         <f t="array" ref="E37">_xlfn.IFS(D37&gt;=90%,7.5,D37&gt;=80%,6,D37&gt;=70%,4.5,D37&gt;=60%,3,D37&lt;60%,0)</f>
@@ -2902,8 +3044,12 @@
       <c r="M37" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
+      <c r="N37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -2934,7 +3080,7 @@
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D37">
+  <conditionalFormatting sqref="D4:D37">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="between">
       <formula>0.6</formula>
       <formula>0.79</formula>
@@ -2969,8 +3115,8 @@
     <col min="3" max="3" width="34" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>

--- a/TFD 3-2/Regular Assessment TFD 3-2.xlsx
+++ b/TFD 3-2/Regular Assessment TFD 3-2.xlsx
@@ -8,16 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ACFB45-9F72-4028-A14D-CDB96C0B8E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B11714-F56E-4C33-A149-285217618D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TFD 3-2 Attendance" sheetId="5" r:id="rId1"/>
-    <sheet name="Assessment" sheetId="6" r:id="rId2"/>
+    <sheet name="Assignment" sheetId="6" r:id="rId2"/>
+    <sheet name="Class Test" sheetId="7" r:id="rId3"/>
+    <sheet name="Eval." sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assignment!$A$3:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Class Test'!$A$3:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Eval.!$A$3:$C$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TFD 3-2 Attendance'!$A$3:$J$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -61,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="60">
   <si>
     <t>SL</t>
   </si>
@@ -210,21 +214,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Fancy Weave</t>
-  </si>
-  <si>
-    <t>Presentation 1</t>
-  </si>
-  <si>
-    <t>Presentation 2</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Color &amp; Weave Effects</t>
-  </si>
-  <si>
     <t>JOBAYER AHAMMAED</t>
   </si>
   <si>
@@ -232,6 +221,30 @@
   </si>
   <si>
     <t>Marks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Full Syllabus</t>
+  </si>
+  <si>
+    <t>NOAS</t>
+  </si>
+  <si>
+    <t>Class Test</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>Assignment</t>
+  </si>
+  <si>
+    <t>NOCT</t>
+  </si>
+  <si>
+    <t>BOEV</t>
   </si>
 </sst>
 </file>
@@ -241,7 +254,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,8 +301,22 @@
       <name val="Gill Sans MT"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,19 +360,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -355,8 +370,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -379,12 +412,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -422,22 +481,31 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -816,12 +884,15 @@
     <col min="12" max="12" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="36.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="25" width="16.21875" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="2"/>
+    <col min="15" max="16" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.88671875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="20" style="2" customWidth="1"/>
+    <col min="19" max="19" width="19.77734375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="22" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>37</v>
       </c>
@@ -850,35 +921,32 @@
         <v>44</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>44</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="7"/>
+      <c r="P1" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
       <c r="S1" s="7"/>
       <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="6">
-        <f>COUNT(A4:A36)</f>
-        <v>33</v>
+        <f>COUNT(A4:A37)</f>
+        <v>34</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>41</v>
@@ -893,7 +961,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="8">
-        <f t="shared" ref="H2:Y2" si="0">G2+1</f>
+        <f t="shared" ref="H2:T2" si="0">G2+1</f>
         <v>3</v>
       </c>
       <c r="I2" s="8">
@@ -944,28 +1012,8 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="U2" s="8">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="V2" s="8">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="W2" s="8">
-        <f>V2+1</f>
-        <v>18</v>
-      </c>
-      <c r="X2" s="8">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="Y2" s="8">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -979,7 +1027,7 @@
         <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F3" s="4">
         <v>46258</v>
@@ -1011,18 +1059,15 @@
       <c r="O3" s="4">
         <v>46285</v>
       </c>
-      <c r="P3" s="4"/>
+      <c r="P3" s="4">
+        <v>46292</v>
+      </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1033,8 +1078,8 @@
         <v>4</v>
       </c>
       <c r="D4" s="10">
-        <f t="shared" ref="D4:D37" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.9</v>
+        <f t="shared" ref="D4:D37" si="1">COUNTIF(F4:T4,"P")/(COUNTIF(F4:T4,"P")+COUNTIF(F4:T4,"A"))</f>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
@@ -1070,18 +1115,15 @@
       <c r="O4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="1"/>
+      <c r="P4" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f>A4+1</f>
         <v>2</v>
@@ -1094,7 +1136,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
@@ -1130,18 +1172,15 @@
       <c r="O5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="1"/>
+      <c r="P5" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A37" si="2">A5+1</f>
         <v>3</v>
@@ -1154,7 +1193,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
@@ -1190,18 +1229,15 @@
       <c r="O6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -1214,7 +1250,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E7" s="1" cm="1">
         <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
@@ -1250,18 +1286,15 @@
       <c r="O7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P7" s="1"/>
+      <c r="P7" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1274,7 +1307,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E8" s="1" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
@@ -1310,18 +1343,15 @@
       <c r="O8" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P8" s="1"/>
+      <c r="P8" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1334,7 +1364,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
@@ -1370,18 +1400,15 @@
       <c r="O9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P9" s="1"/>
+      <c r="P9" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -1394,7 +1421,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1430,19 +1457,16 @@
       <c r="O10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P10" s="1"/>
+      <c r="P10" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A11" s="16">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -1454,7 +1478,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="E11" s="1" cm="1">
         <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
@@ -1490,18 +1514,15 @@
       <c r="O11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -1550,18 +1571,15 @@
       <c r="O12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P12" s="1"/>
+      <c r="P12" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -1574,7 +1592,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="E13" s="1" cm="1">
         <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
@@ -1610,18 +1628,15 @@
       <c r="O13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P13" s="1"/>
+      <c r="P13" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1634,7 +1649,7 @@
       </c>
       <c r="D14" s="10">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
@@ -1670,18 +1685,15 @@
       <c r="O14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P14" s="1"/>
+      <c r="P14" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -1694,7 +1706,7 @@
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="E15" s="1" cm="1">
         <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
@@ -1730,18 +1742,15 @@
       <c r="O15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P15" s="1"/>
+      <c r="P15" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -1754,7 +1763,7 @@
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E16" s="1" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
@@ -1790,18 +1799,15 @@
       <c r="O16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P16" s="1"/>
+      <c r="P16" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -1850,18 +1856,15 @@
       <c r="O17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P17" s="1"/>
+      <c r="P17" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1874,7 +1877,7 @@
       </c>
       <c r="D18" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
@@ -1910,18 +1913,15 @@
       <c r="O18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P18" s="1"/>
+      <c r="P18" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="D19" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1970,18 +1970,15 @@
       <c r="O19" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P19" s="1"/>
+      <c r="P19" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -1994,7 +1991,7 @@
       </c>
       <c r="D20" s="10">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E20" s="1" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
@@ -2030,18 +2027,15 @@
       <c r="O20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P20" s="1"/>
+      <c r="P20" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -2054,7 +2048,7 @@
       </c>
       <c r="D21" s="10">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="E21" s="1" cm="1">
         <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
@@ -2090,18 +2084,15 @@
       <c r="O21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P21" s="1"/>
+      <c r="P21" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -2114,7 +2105,7 @@
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E22" s="1" cm="1">
         <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
@@ -2150,18 +2141,15 @@
       <c r="O22" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P22" s="1"/>
+      <c r="P22" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -2174,7 +2162,7 @@
       </c>
       <c r="D23" s="10">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
@@ -2210,18 +2198,15 @@
       <c r="O23" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P23" s="1"/>
+      <c r="P23" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -2234,11 +2219,11 @@
       </c>
       <c r="D24" s="10">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>39</v>
@@ -2270,18 +2255,15 @@
       <c r="O24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P24" s="1"/>
+      <c r="P24" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -2294,7 +2276,7 @@
       </c>
       <c r="D25" s="10">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
@@ -2330,18 +2312,15 @@
       <c r="O25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P25" s="1"/>
+      <c r="P25" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2354,7 +2333,7 @@
       </c>
       <c r="D26" s="10">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E26" s="1" cm="1">
         <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
@@ -2390,18 +2369,15 @@
       <c r="O26" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P26" s="1"/>
+      <c r="P26" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2414,7 +2390,7 @@
       </c>
       <c r="D27" s="10">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
@@ -2450,18 +2426,15 @@
       <c r="O27" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P27" s="1"/>
+      <c r="P27" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2474,7 +2447,7 @@
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
@@ -2510,18 +2483,15 @@
       <c r="O28" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P28" s="1"/>
+      <c r="P28" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2534,11 +2504,11 @@
       </c>
       <c r="D29" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>39</v>
@@ -2570,18 +2540,15 @@
       <c r="O29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P29" s="1"/>
+      <c r="P29" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2594,7 +2561,7 @@
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
@@ -2630,18 +2597,15 @@
       <c r="O30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P30" s="1"/>
+      <c r="P30" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2654,7 +2618,7 @@
       </c>
       <c r="D31" s="10">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
@@ -2690,18 +2654,15 @@
       <c r="O31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P31" s="1"/>
+      <c r="P31" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -2750,18 +2711,15 @@
       <c r="O32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P32" s="1"/>
+      <c r="P32" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -2774,7 +2732,7 @@
       </c>
       <c r="D33" s="10">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="E33" s="1" cm="1">
         <f t="array" ref="E33">_xlfn.IFS(D33&gt;=90%,7.5,D33&gt;=80%,6,D33&gt;=70%,4.5,D33&gt;=60%,3,D33&lt;60%,0)</f>
@@ -2810,18 +2768,15 @@
       <c r="O33" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P33" s="1"/>
+      <c r="P33" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -2834,7 +2789,7 @@
       </c>
       <c r="D34" s="10">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="E34" s="1" cm="1">
         <f t="array" ref="E34">_xlfn.IFS(D34&gt;=90%,7.5,D34&gt;=80%,6,D34&gt;=70%,4.5,D34&gt;=60%,3,D34&lt;60%,0)</f>
@@ -2870,18 +2825,15 @@
       <c r="O34" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P34" s="1"/>
+      <c r="P34" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -2894,7 +2846,7 @@
       </c>
       <c r="D35" s="10">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
@@ -2930,18 +2882,15 @@
       <c r="O35" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P35" s="1"/>
+      <c r="P35" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -2954,11 +2903,11 @@
       </c>
       <c r="D36" s="10">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="E36" s="1" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>40</v>
@@ -2990,18 +2939,15 @@
       <c r="O36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P36" s="1"/>
+      <c r="P36" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -3010,11 +2956,11 @@
         <v>202116031</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="E37" s="1" cm="1">
         <f t="array" ref="E37">_xlfn.IFS(D37&gt;=90%,7.5,D37&gt;=80%,6,D37&gt;=70%,4.5,D37&gt;=60%,3,D37&lt;60%,0)</f>
@@ -3050,16 +2996,18 @@
       <c r="O37" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="P37" s="1"/>
+      <c r="P37" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="P38" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:J3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -3079,8 +3027,6 @@
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>0.6</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D37">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="between">
       <formula>0.6</formula>
       <formula>0.79</formula>
@@ -3107,16 +3053,1018 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D46E0EB-0A5B-4A3E-A8DB-6970DA5B0FF6}">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="6">
+        <f>COUNT(A4:A37)</f>
+        <v>34</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="15">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>23010601001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="13"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f>A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>23010601002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="13"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" ref="A6:A37" si="0">A5+1</f>
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>23010601003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="13"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>23010601004</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>23010601005</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>23010601006</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="13"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23010601007</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="13"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23010601008</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="13"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>23010601009</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="13"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>23010601010</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>23010601011</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="13"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>23010601012</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>23010601013</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="13"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>23010601016</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>23010601017</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="13"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>23010601018</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="13"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>23010601020</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>23010601021</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="13"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>23010601022</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>23010601025</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="13"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>23010601026</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>23010601027</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="13"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>23010601028</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="13"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>23010601029</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="13"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>23010601030</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>23010601031</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>23010601032</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="13"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>23010601033</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="13"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="1">
+        <v>23010601034</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="1">
+        <v>23010601035</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="1">
+        <v>22010601014</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="1">
+        <v>22010601031</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="1">
+        <v>22010601034</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>202116031</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="1"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C0D1566-2492-495A-94E6-774C4918A752}">
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="6">
+        <f>COUNT(A4:A37)</f>
+        <v>34</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>23010601001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="13"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f>A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>23010601002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="13"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" ref="A6:A37" si="0">A5+1</f>
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>23010601003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="13"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>23010601004</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>23010601005</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>23010601006</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="13"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23010601007</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="13"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23010601008</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="13"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>23010601009</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="13"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>23010601010</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>23010601011</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="13"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>23010601012</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>23010601013</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="13"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>23010601016</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>23010601017</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="13"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>23010601018</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="13"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>23010601020</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>23010601021</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="13"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>23010601022</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>23010601025</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="13"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>23010601026</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>23010601027</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="13"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>23010601028</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="13"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>23010601029</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="13"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>23010601030</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>23010601031</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>23010601032</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="13"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>23010601033</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="13"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="1">
+        <v>23010601034</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="1">
+        <v>23010601035</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="1">
+        <v>22010601014</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="1">
+        <v>22010601031</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="1">
+        <v>22010601034</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>202116031</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="1"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239D01B9-9199-495E-8374-2B72AF9E58A5}">
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="23.21875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -3128,36 +4076,34 @@
       <c r="C1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="18"/>
+      <c r="D1" s="18">
+        <v>7.5</v>
+      </c>
+      <c r="E1" s="18">
+        <v>7.5</v>
+      </c>
+      <c r="F1" s="18">
+        <v>15</v>
+      </c>
+      <c r="G1" s="20">
+        <v>30</v>
+      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="6">
-        <f>COUNT(A4:A36)</f>
-        <v>33</v>
+        <f>COUNT(A4:A37)</f>
+        <v>34</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+        <v>59</v>
+      </c>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -3169,17 +4115,17 @@
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="14">
-        <v>20</v>
-      </c>
-      <c r="G3" s="14">
-        <v>7.5</v>
+      <c r="D3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3192,15 +4138,21 @@
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15">
-        <f t="shared" ref="F4:F36" si="0">SUM(D4:E4)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="15">
-        <f>(F4/20)*7.5</f>
-        <v>0</v>
+      <c r="D4" s="13">
+        <f>_xlfn.XLOOKUP(B4,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E4" s="13">
+        <f>_xlfn.XLOOKUP(B4,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="13">
+        <f>_xlfn.XLOOKUP(B4,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="16">
+        <f>CEILING(SUM(D4:F4),0.5)</f>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3214,20 +4166,26 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="15">
-        <f t="shared" ref="G5:G36" si="1">(F5/20)*7.5</f>
-        <v>0</v>
+      <c r="D5" s="13">
+        <f>_xlfn.XLOOKUP(B5,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E5" s="13">
+        <f>_xlfn.XLOOKUP(B5,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="13">
+        <f>_xlfn.XLOOKUP(B5,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="16">
+        <f t="shared" ref="G5:G37" si="0">CEILING(SUM(D5:F5),0.5)</f>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A36" si="2">A5+1</f>
+        <f t="shared" ref="A6:A37" si="1">A5+1</f>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -3236,20 +4194,26 @@
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D6" s="13">
+        <f>_xlfn.XLOOKUP(B6,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E6" s="13">
+        <f>_xlfn.XLOOKUP(B6,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="13">
+        <f>_xlfn.XLOOKUP(B6,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B7" s="1">
@@ -3258,20 +4222,26 @@
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D7" s="13">
+        <f>_xlfn.XLOOKUP(B7,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E7" s="13">
+        <f>_xlfn.XLOOKUP(B7,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="13">
+        <f>_xlfn.XLOOKUP(B7,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -3280,20 +4250,26 @@
       <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D8" s="13">
+        <f>_xlfn.XLOOKUP(B8,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E8" s="13">
+        <f>_xlfn.XLOOKUP(B8,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="13">
+        <f>_xlfn.XLOOKUP(B8,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B9" s="1">
@@ -3302,20 +4278,26 @@
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D9" s="13">
+        <f>_xlfn.XLOOKUP(B9,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E9" s="13">
+        <f>_xlfn.XLOOKUP(B9,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
+        <f>_xlfn.XLOOKUP(B9,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -3324,20 +4306,26 @@
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D10" s="13">
+        <f>_xlfn.XLOOKUP(B10,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E10" s="13">
+        <f>_xlfn.XLOOKUP(B10,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="13">
+        <f>_xlfn.XLOOKUP(B10,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="16">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B11" s="1">
@@ -3346,20 +4334,26 @@
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="15">
-        <f t="shared" si="1"/>
+      <c r="D11" s="13">
+        <f>_xlfn.XLOOKUP(B11,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="13">
+        <f>_xlfn.XLOOKUP(B11,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="13">
+        <f>_xlfn.XLOOKUP(B11,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B12" s="1">
@@ -3368,20 +4362,26 @@
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D12" s="13">
+        <f>_xlfn.XLOOKUP(B12,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E12" s="13">
+        <f>_xlfn.XLOOKUP(B12,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <f>_xlfn.XLOOKUP(B12,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
@@ -3390,20 +4390,26 @@
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="15">
-        <f t="shared" si="1"/>
+      <c r="D13" s="13">
+        <f>_xlfn.XLOOKUP(B13,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="13">
+        <f>_xlfn.XLOOKUP(B13,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="13">
+        <f>_xlfn.XLOOKUP(B13,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B14" s="1">
@@ -3412,20 +4418,26 @@
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D14" s="13">
+        <f>_xlfn.XLOOKUP(B14,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E14" s="13">
+        <f>_xlfn.XLOOKUP(B14,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
+        <f>_xlfn.XLOOKUP(B14,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
-        <f t="shared" si="2"/>
+      <c r="A15" s="1">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="B15" s="1">
@@ -3434,20 +4446,26 @@
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D15" s="13">
+        <f>_xlfn.XLOOKUP(B15,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>3</v>
+      </c>
+      <c r="E15" s="13">
+        <f>_xlfn.XLOOKUP(B15,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="13">
+        <f>_xlfn.XLOOKUP(B15,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="16">
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B16" s="1">
@@ -3456,20 +4474,26 @@
       <c r="C16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D16" s="13">
+        <f>_xlfn.XLOOKUP(B16,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E16" s="13">
+        <f>_xlfn.XLOOKUP(B16,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
+        <f>_xlfn.XLOOKUP(B16,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B17" s="1">
@@ -3478,20 +4502,26 @@
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D17" s="13">
+        <f>_xlfn.XLOOKUP(B17,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E17" s="13">
+        <f>_xlfn.XLOOKUP(B17,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="13">
+        <f>_xlfn.XLOOKUP(B17,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B18" s="1">
@@ -3500,20 +4530,26 @@
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="15">
-        <f t="shared" si="1"/>
+      <c r="D18" s="13">
+        <f>_xlfn.XLOOKUP(B18,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="13">
+        <f>_xlfn.XLOOKUP(B18,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="13">
+        <f>_xlfn.XLOOKUP(B18,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B19" s="1">
@@ -3522,20 +4558,26 @@
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D19" s="13">
+        <f>_xlfn.XLOOKUP(B19,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>6</v>
+      </c>
+      <c r="E19" s="13">
+        <f>_xlfn.XLOOKUP(B19,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="13">
+        <f>_xlfn.XLOOKUP(B19,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="16">
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -3544,20 +4586,26 @@
       <c r="C20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D20" s="13">
+        <f>_xlfn.XLOOKUP(B20,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E20" s="13">
+        <f>_xlfn.XLOOKUP(B20,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
+        <f>_xlfn.XLOOKUP(B20,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B21" s="1">
@@ -3566,20 +4614,26 @@
       <c r="C21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D21" s="13">
+        <f>_xlfn.XLOOKUP(B21,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E21" s="13">
+        <f>_xlfn.XLOOKUP(B21,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
+        <f>_xlfn.XLOOKUP(B21,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B22" s="1">
@@ -3588,20 +4642,26 @@
       <c r="C22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D22" s="13">
+        <f>_xlfn.XLOOKUP(B22,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E22" s="13">
+        <f>_xlfn.XLOOKUP(B22,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
+        <f>_xlfn.XLOOKUP(B22,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="16">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="B23" s="1">
@@ -3610,20 +4670,26 @@
       <c r="C23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D23" s="13">
+        <f>_xlfn.XLOOKUP(B23,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E23" s="13">
+        <f>_xlfn.XLOOKUP(B23,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="13">
+        <f>_xlfn.XLOOKUP(B23,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="16">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="B24" s="1">
@@ -3632,20 +4698,26 @@
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="15">
-        <f t="shared" si="1"/>
+      <c r="D24" s="13">
+        <f>_xlfn.XLOOKUP(B24,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="13">
+        <f>_xlfn.XLOOKUP(B24,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="13">
+        <f>_xlfn.XLOOKUP(B24,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="B25" s="1">
@@ -3654,20 +4726,26 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D25" s="13">
+        <f>_xlfn.XLOOKUP(B25,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E25" s="13">
+        <f>_xlfn.XLOOKUP(B25,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="13">
+        <f>_xlfn.XLOOKUP(B25,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="16">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B26" s="1">
@@ -3676,20 +4754,26 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D26" s="13">
+        <f>_xlfn.XLOOKUP(B26,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E26" s="13">
+        <f>_xlfn.XLOOKUP(B26,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="13">
+        <f>_xlfn.XLOOKUP(B26,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="16">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="B27" s="1">
@@ -3698,20 +4782,26 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="15">
-        <f t="shared" si="1"/>
+      <c r="D27" s="13">
+        <f>_xlfn.XLOOKUP(B27,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="13">
+        <f>_xlfn.XLOOKUP(B27,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="13">
+        <f>_xlfn.XLOOKUP(B27,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B28" s="1">
@@ -3720,20 +4810,26 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D28" s="13">
+        <f>_xlfn.XLOOKUP(B28,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E28" s="13">
+        <f>_xlfn.XLOOKUP(B28,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
+        <f>_xlfn.XLOOKUP(B28,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="16">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="B29" s="1">
@@ -3742,20 +4838,26 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D29" s="13">
+        <f>_xlfn.XLOOKUP(B29,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E29" s="13">
+        <f>_xlfn.XLOOKUP(B29,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="13">
+        <f>_xlfn.XLOOKUP(B29,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="16">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="B30" s="1">
@@ -3764,20 +4866,26 @@
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D30" s="13">
+        <f>_xlfn.XLOOKUP(B30,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E30" s="13">
+        <f>_xlfn.XLOOKUP(B30,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="13">
+        <f>_xlfn.XLOOKUP(B30,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="16">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="B31" s="1">
@@ -3786,20 +4894,26 @@
       <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="15">
-        <f t="shared" si="1"/>
+      <c r="D31" s="13">
+        <f>_xlfn.XLOOKUP(B31,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="13">
+        <f>_xlfn.XLOOKUP(B31,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="13">
+        <f>_xlfn.XLOOKUP(B31,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="B32" s="1">
@@ -3808,20 +4922,26 @@
       <c r="C32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D32" s="13">
+        <f>_xlfn.XLOOKUP(B32,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E32" s="13">
+        <f>_xlfn.XLOOKUP(B32,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="13">
+        <f>_xlfn.XLOOKUP(B32,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="16">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="B33" s="1">
@@ -3830,20 +4950,26 @@
       <c r="C33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D33" s="13">
+        <f>_xlfn.XLOOKUP(B33,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>6</v>
+      </c>
+      <c r="E33" s="13">
+        <f>_xlfn.XLOOKUP(B33,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="13">
+        <f>_xlfn.XLOOKUP(B33,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="16">
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="B34" s="1">
@@ -3852,20 +4978,26 @@
       <c r="C34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D34" s="13">
+        <f>_xlfn.XLOOKUP(B34,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>3</v>
+      </c>
+      <c r="E34" s="13">
+        <f>_xlfn.XLOOKUP(B34,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="13">
+        <f>_xlfn.XLOOKUP(B34,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="16">
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="B35" s="1">
@@ -3874,20 +5006,26 @@
       <c r="C35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="D35" s="13">
+        <f>_xlfn.XLOOKUP(B35,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>3</v>
+      </c>
+      <c r="E35" s="13">
+        <f>_xlfn.XLOOKUP(B35,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="13">
+        <f>_xlfn.XLOOKUP(B35,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="16">
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="B36" s="1">
@@ -3896,26 +5034,60 @@
       <c r="C36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="15">
-        <f t="shared" si="1"/>
+      <c r="D36" s="13">
+        <f>_xlfn.XLOOKUP(B36,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>3</v>
+      </c>
+      <c r="E36" s="13">
+        <f>_xlfn.XLOOKUP(B36,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="13">
+        <f>_xlfn.XLOOKUP(B36,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="16">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>202116031</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="13">
+        <f>_xlfn.XLOOKUP(B37,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="13">
+        <f>_xlfn.XLOOKUP(B37,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="13">
+        <f>_xlfn.XLOOKUP(B37,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="16">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:G2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3:E3" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/TFD 3-2/Regular Assessment TFD 3-2.xlsx
+++ b/TFD 3-2/Regular Assessment TFD 3-2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TFD 3-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B11714-F56E-4C33-A149-285217618D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074EA3AC-97BC-4184-B9EA-D16742F87CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TFD 3-2 Attendance" sheetId="5" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="60">
   <si>
     <t>SL</t>
   </si>
@@ -885,7 +885,7 @@
     <col min="13" max="13" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="36.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="36.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20" style="2" customWidth="1"/>
     <col min="19" max="19" width="19.77734375" style="2" customWidth="1"/>
     <col min="20" max="20" width="22" style="2" customWidth="1"/>
@@ -1062,7 +1062,9 @@
       <c r="P3" s="4">
         <v>46292</v>
       </c>
-      <c r="Q3" s="4"/>
+      <c r="Q3" s="4">
+        <v>46295</v>
+      </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -1079,7 +1081,7 @@
       </c>
       <c r="D4" s="10">
         <f t="shared" ref="D4:D37" si="1">COUNTIF(F4:T4,"P")/(COUNTIF(F4:T4,"P")+COUNTIF(F4:T4,"A"))</f>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
@@ -1118,7 +1120,9 @@
       <c r="P4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -1136,7 +1140,7 @@
       </c>
       <c r="D5" s="10">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
@@ -1175,7 +1179,9 @@
       <c r="P5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -1193,7 +1199,7 @@
       </c>
       <c r="D6" s="10">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
@@ -1232,7 +1238,9 @@
       <c r="P6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -1250,7 +1258,7 @@
       </c>
       <c r="D7" s="10">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E7" s="1" cm="1">
         <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
@@ -1289,7 +1297,9 @@
       <c r="P7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -1307,7 +1317,7 @@
       </c>
       <c r="D8" s="10">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E8" s="1" cm="1">
         <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
@@ -1346,7 +1356,9 @@
       <c r="P8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -1364,7 +1376,7 @@
       </c>
       <c r="D9" s="10">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
@@ -1403,7 +1415,9 @@
       <c r="P9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q9" s="1"/>
+      <c r="Q9" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1421,7 +1435,7 @@
       </c>
       <c r="D10" s="10">
         <f t="shared" si="1"/>
-        <v>0.72727272727272729</v>
+        <v>0.75</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1460,7 +1474,9 @@
       <c r="P10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q10" s="1"/>
+      <c r="Q10" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1478,7 +1494,7 @@
       </c>
       <c r="D11" s="10">
         <f t="shared" si="1"/>
-        <v>0.45454545454545453</v>
+        <v>0.5</v>
       </c>
       <c r="E11" s="1" cm="1">
         <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
@@ -1517,7 +1533,9 @@
       <c r="P11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="Q11" s="1"/>
+      <c r="Q11" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1574,7 +1592,9 @@
       <c r="P12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q12" s="1"/>
+      <c r="Q12" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -1592,7 +1612,7 @@
       </c>
       <c r="D13" s="10">
         <f t="shared" si="1"/>
-        <v>0.45454545454545453</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="1" cm="1">
         <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
@@ -1631,7 +1651,9 @@
       <c r="P13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q13" s="1"/>
+      <c r="Q13" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
@@ -1649,7 +1671,7 @@
       </c>
       <c r="D14" s="10">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
@@ -1688,7 +1710,9 @@
       <c r="P14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -1706,7 +1730,7 @@
       </c>
       <c r="D15" s="10">
         <f t="shared" si="1"/>
-        <v>0.63636363636363635</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E15" s="1" cm="1">
         <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
@@ -1745,7 +1769,9 @@
       <c r="P15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q15" s="1"/>
+      <c r="Q15" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1763,7 +1789,7 @@
       </c>
       <c r="D16" s="10">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E16" s="1" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
@@ -1802,7 +1828,9 @@
       <c r="P16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q16" s="1"/>
+      <c r="Q16" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1859,7 +1887,9 @@
       <c r="P17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q17" s="1"/>
+      <c r="Q17" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1877,7 +1907,7 @@
       </c>
       <c r="D18" s="10">
         <f t="shared" si="1"/>
-        <v>0.54545454545454541</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
@@ -1916,7 +1946,9 @@
       <c r="P18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q18" s="1"/>
+      <c r="Q18" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
@@ -1934,7 +1966,7 @@
       </c>
       <c r="D19" s="10">
         <f t="shared" si="1"/>
-        <v>0.81818181818181823</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1973,7 +2005,9 @@
       <c r="P19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -1991,7 +2025,7 @@
       </c>
       <c r="D20" s="10">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E20" s="1" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
@@ -2030,7 +2064,9 @@
       <c r="P20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q20" s="1"/>
+      <c r="Q20" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
@@ -2048,7 +2084,7 @@
       </c>
       <c r="D21" s="10">
         <f t="shared" si="1"/>
-        <v>0.90909090909090906</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="E21" s="1" cm="1">
         <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
@@ -2087,7 +2123,9 @@
       <c r="P21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q21" s="1"/>
+      <c r="Q21" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
@@ -2105,7 +2143,7 @@
       </c>
       <c r="D22" s="10">
         <f t="shared" si="1"/>
-        <v>0.72727272727272729</v>
+        <v>0.75</v>
       </c>
       <c r="E22" s="1" cm="1">
         <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
@@ -2144,7 +2182,9 @@
       <c r="P22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q22" s="1"/>
+      <c r="Q22" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -2162,7 +2202,7 @@
       </c>
       <c r="D23" s="10">
         <f t="shared" si="1"/>
-        <v>0.72727272727272729</v>
+        <v>0.75</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
@@ -2201,7 +2241,9 @@
       <c r="P23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q23" s="1"/>
+      <c r="Q23" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -2219,7 +2261,7 @@
       </c>
       <c r="D24" s="10">
         <f t="shared" si="1"/>
-        <v>0.54545454545454541</v>
+        <v>0.5</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
@@ -2258,7 +2300,9 @@
       <c r="P24" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="Q24" s="1"/>
+      <c r="Q24" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
@@ -2276,7 +2320,7 @@
       </c>
       <c r="D25" s="10">
         <f t="shared" si="1"/>
-        <v>0.72727272727272729</v>
+        <v>0.75</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
@@ -2315,7 +2359,9 @@
       <c r="P25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q25" s="1"/>
+      <c r="Q25" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
@@ -2333,7 +2379,7 @@
       </c>
       <c r="D26" s="10">
         <f t="shared" si="1"/>
-        <v>0.72727272727272729</v>
+        <v>0.75</v>
       </c>
       <c r="E26" s="1" cm="1">
         <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
@@ -2372,7 +2418,9 @@
       <c r="P26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q26" s="1"/>
+      <c r="Q26" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
@@ -2390,7 +2438,7 @@
       </c>
       <c r="D27" s="10">
         <f t="shared" si="1"/>
-        <v>0.36363636363636365</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
@@ -2429,7 +2477,9 @@
       <c r="P27" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="Q27" s="1"/>
+      <c r="Q27" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
@@ -2447,7 +2497,7 @@
       </c>
       <c r="D28" s="10">
         <f t="shared" si="1"/>
-        <v>0.72727272727272729</v>
+        <v>0.75</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
@@ -2486,7 +2536,9 @@
       <c r="P28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q28" s="1"/>
+      <c r="Q28" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
@@ -2504,7 +2556,7 @@
       </c>
       <c r="D29" s="10">
         <f t="shared" si="1"/>
-        <v>0.72727272727272729</v>
+        <v>0.75</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
@@ -2543,7 +2595,9 @@
       <c r="P29" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="Q29" s="1"/>
+      <c r="Q29" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
@@ -2561,7 +2615,7 @@
       </c>
       <c r="D30" s="10">
         <f t="shared" si="1"/>
-        <v>0.72727272727272729</v>
+        <v>0.75</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
@@ -2600,7 +2654,9 @@
       <c r="P30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q30" s="1"/>
+      <c r="Q30" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
@@ -2618,7 +2674,7 @@
       </c>
       <c r="D31" s="10">
         <f t="shared" si="1"/>
-        <v>0.36363636363636365</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
@@ -2657,7 +2713,9 @@
       <c r="P31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="Q31" s="1"/>
+      <c r="Q31" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
@@ -2714,7 +2772,9 @@
       <c r="P32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q32" s="1"/>
+      <c r="Q32" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
@@ -2732,7 +2792,7 @@
       </c>
       <c r="D33" s="10">
         <f t="shared" si="1"/>
-        <v>0.81818181818181823</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E33" s="1" cm="1">
         <f t="array" ref="E33">_xlfn.IFS(D33&gt;=90%,7.5,D33&gt;=80%,6,D33&gt;=70%,4.5,D33&gt;=60%,3,D33&lt;60%,0)</f>
@@ -2771,7 +2831,9 @@
       <c r="P33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q33" s="1"/>
+      <c r="Q33" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -2789,7 +2851,7 @@
       </c>
       <c r="D34" s="10">
         <f t="shared" si="1"/>
-        <v>0.63636363636363635</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E34" s="1" cm="1">
         <f t="array" ref="E34">_xlfn.IFS(D34&gt;=90%,7.5,D34&gt;=80%,6,D34&gt;=70%,4.5,D34&gt;=60%,3,D34&lt;60%,0)</f>
@@ -2828,7 +2890,9 @@
       <c r="P34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
@@ -2846,11 +2910,11 @@
       </c>
       <c r="D35" s="10">
         <f t="shared" si="1"/>
-        <v>0.63636363636363635</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>39</v>
@@ -2885,7 +2949,9 @@
       <c r="P35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q35" s="1"/>
+      <c r="Q35" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
@@ -2903,7 +2969,7 @@
       </c>
       <c r="D36" s="10">
         <f t="shared" si="1"/>
-        <v>0.63636363636363635</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E36" s="1" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
@@ -2942,7 +3008,9 @@
       <c r="P36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="Q36" s="1"/>
+      <c r="Q36" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
@@ -2960,7 +3028,7 @@
       </c>
       <c r="D37" s="10">
         <f t="shared" si="1"/>
-        <v>0.18181818181818182</v>
+        <v>0.25</v>
       </c>
       <c r="E37" s="1" cm="1">
         <f t="array" ref="E37">_xlfn.IFS(D37&gt;=90%,7.5,D37&gt;=80%,6,D37&gt;=70%,4.5,D37&gt;=60%,3,D37&lt;60%,0)</f>
@@ -2999,7 +3067,9 @@
       <c r="P37" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="Q37" s="1"/>
+      <c r="Q37" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
@@ -3114,7 +3184,9 @@
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="13"/>
+      <c r="D4" s="13">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
@@ -4144,7 +4216,7 @@
       </c>
       <c r="E4" s="13">
         <f>_xlfn.XLOOKUP(B4,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4" s="13">
         <f>_xlfn.XLOOKUP(B4,'Class Test'!$B$4:$B$37,'Class Test'!$D$4:$D$37)</f>
@@ -4152,7 +4224,7 @@
       </c>
       <c r="G4" s="16">
         <f>CEILING(SUM(D4:F4),0.5)</f>
-        <v>7.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -5008,7 +5080,7 @@
       </c>
       <c r="D35" s="13">
         <f>_xlfn.XLOOKUP(B35,'TFD 3-2 Attendance'!$B$4:$B$37,'TFD 3-2 Attendance'!$E$4:$E$37)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E35" s="13">
         <f>_xlfn.XLOOKUP(B35,Assignment!$B$4:$B$37,Assignment!$D$4:$D$37)</f>
@@ -5020,7 +5092,7 @@
       </c>
       <c r="G35" s="16">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
